--- a/AAII_Financials/Quarterly/SCNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>SCNI</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
-      </c>
-      <c r="G7" s="2">
-        <v>45747</v>
       </c>
       <c r="H7" s="2">
         <v>45657</v>
@@ -716,51 +716,54 @@
         <v>45291</v>
       </c>
       <c r="K7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E8" s="3">
         <v>300</v>
       </c>
       <c r="F8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
@@ -789,8 +792,8 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -801,13 +804,16 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="E9" s="3">
         <v>1000</v>
@@ -816,7 +822,7 @@
         <v>1000</v>
       </c>
       <c r="G9" s="3">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -857,22 +863,25 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-700</v>
+        <v>-1300</v>
       </c>
       <c r="E10" s="3">
         <v>-700</v>
       </c>
       <c r="F10" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="G10" s="3">
-        <v>-600</v>
+        <v>-1500</v>
       </c>
       <c r="H10" s="3">
         <v>-200</v>
@@ -913,8 +922,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,13 +947,14 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>600</v>
@@ -950,7 +963,7 @@
         <v>600</v>
       </c>
       <c r="G12" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="H12" s="3">
         <v>1300</v>
@@ -962,37 +975,40 @@
         <v>600</v>
       </c>
       <c r="K12" s="3">
+        <v>600</v>
+      </c>
+      <c r="L12" s="3">
         <v>1500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1047,13 +1063,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1088,8 +1107,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1103,13 +1122,16 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
@@ -1136,16 +1158,16 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1159,8 +1181,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1178,22 +1203,23 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="E17" s="3">
         <v>2200</v>
       </c>
       <c r="F17" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="G17" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H17" s="3">
         <v>2500</v>
@@ -1205,42 +1231,45 @@
         <v>1800</v>
       </c>
       <c r="K17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1900</v>
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
         <v>-1900</v>
@@ -1249,7 +1278,7 @@
         <v>-1900</v>
       </c>
       <c r="G18" s="3">
-        <v>-1900</v>
+        <v>-2200</v>
       </c>
       <c r="H18" s="3">
         <v>-2300</v>
@@ -1261,37 +1290,40 @@
         <v>-1800</v>
       </c>
       <c r="K18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1312,19 +1344,20 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>200</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="F20" s="3">
+        <v>200</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
@@ -1338,8 +1371,8 @@
       <c r="J20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>-3100</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1356,34 +1389,37 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>6900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="E21" s="3">
         <v>-1700</v>
       </c>
       <c r="F21" s="3">
-        <v>-1500</v>
+        <v>-1700</v>
       </c>
       <c r="G21" s="3">
-        <v>-1500</v>
+        <v>-1800</v>
       </c>
       <c r="H21" s="3">
         <v>-16600</v>
@@ -1395,51 +1431,54 @@
         <v>1300</v>
       </c>
       <c r="K21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>5200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1451,23 +1490,23 @@
         <v>3800</v>
       </c>
       <c r="K22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1480,13 +1519,16 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E23" s="3">
         <v>-2100</v>
@@ -1495,7 +1537,7 @@
         <v>-2100</v>
       </c>
       <c r="G23" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H23" s="3">
         <v>-2200</v>
@@ -1507,37 +1549,40 @@
         <v>-2300</v>
       </c>
       <c r="K23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1577,8 +1622,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1592,8 +1637,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1648,13 +1696,16 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E26" s="3">
         <v>-2100</v>
@@ -1663,7 +1714,7 @@
         <v>-2100</v>
       </c>
       <c r="G26" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H26" s="3">
         <v>-2200</v>
@@ -1675,42 +1726,45 @@
         <v>-2300</v>
       </c>
       <c r="K26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E27" s="3">
         <v>-2100</v>
@@ -1719,7 +1773,7 @@
         <v>-2100</v>
       </c>
       <c r="G27" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H27" s="3">
         <v>-7000</v>
@@ -1731,37 +1785,40 @@
         <v>-2300</v>
       </c>
       <c r="K27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1816,8 +1873,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1872,8 +1932,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1928,8 +1991,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1984,19 +2050,22 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-200</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="F32" s="3">
+        <v>-200</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
@@ -2010,8 +2079,8 @@
       <c r="J32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>3100</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
@@ -2028,25 +2097,28 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-6900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E33" s="3">
         <v>-2100</v>
@@ -2055,7 +2127,7 @@
         <v>-2100</v>
       </c>
       <c r="G33" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H33" s="3">
         <v>-2200</v>
@@ -2067,37 +2139,40 @@
         <v>-2300</v>
       </c>
       <c r="K33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2152,13 +2227,16 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E35" s="3">
         <v>-2100</v>
@@ -2167,7 +2245,7 @@
         <v>-2100</v>
       </c>
       <c r="G35" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H35" s="3">
         <v>-2200</v>
@@ -2179,56 +2257,59 @@
         <v>-2300</v>
       </c>
       <c r="K35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45747</v>
       </c>
       <c r="H38" s="2">
         <v>45657</v>
@@ -2240,37 +2321,40 @@
         <v>45291</v>
       </c>
       <c r="K38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2291,8 +2375,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2313,19 +2398,20 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1700</v>
+        <v>2700</v>
       </c>
       <c r="E41" s="3">
         <v>1700</v>
       </c>
       <c r="F41" s="3">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="G41" s="3">
         <v>1000</v>
@@ -2340,37 +2426,40 @@
         <v>4900</v>
       </c>
       <c r="K41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L41" s="3">
         <v>7500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>7500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>48900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>54000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2425,19 +2514,22 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -2451,8 +2543,8 @@
       <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>400</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -2466,23 +2558,26 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>700</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>600</v>
       </c>
       <c r="R43" s="3">
         <v>600</v>
       </c>
       <c r="S43" s="3">
+        <v>600</v>
+      </c>
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2522,8 +2617,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2537,8 +2632,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2593,19 +2691,22 @@
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="E46" s="3">
         <v>2100</v>
       </c>
       <c r="F46" s="3">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="G46" s="3">
         <v>1500</v>
@@ -2620,37 +2721,40 @@
         <v>5400</v>
       </c>
       <c r="K46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L46" s="3">
         <v>7800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>49500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2690,8 +2794,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2705,19 +2809,22 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9600</v>
+        <v>13700</v>
       </c>
       <c r="E48" s="3">
         <v>9600</v>
       </c>
       <c r="F48" s="3">
-        <v>10300</v>
+        <v>9600</v>
       </c>
       <c r="G48" s="3">
         <v>10300</v>
@@ -2732,37 +2839,40 @@
         <v>12000</v>
       </c>
       <c r="K48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L48" s="3">
         <v>12100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>12100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>45100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>44100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2793,11 +2903,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2817,8 +2927,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2873,8 +2986,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2929,8 +3045,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2970,23 +3089,26 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>1000</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>1000</v>
       </c>
       <c r="R52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S52" s="3">
         <v>900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3041,19 +3163,22 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11600</v>
+        <v>17200</v>
       </c>
       <c r="E54" s="3">
         <v>11600</v>
       </c>
       <c r="F54" s="3">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="G54" s="3">
         <v>11800</v>
@@ -3068,37 +3193,40 @@
         <v>17500</v>
       </c>
       <c r="K54" s="3">
+        <v>17500</v>
+      </c>
+      <c r="L54" s="3">
         <v>19900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>19900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>85600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>95500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>99600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3119,8 +3247,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3141,19 +3270,20 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
       </c>
       <c r="F57" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>700</v>
@@ -3168,48 +3298,51 @@
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
@@ -3229,43 +3362,46 @@
       <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>400</v>
       </c>
       <c r="P58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
@@ -3303,25 +3439,28 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
-        <v>800</v>
+      <c r="S59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T59" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="E60" s="3">
         <v>1600</v>
       </c>
       <c r="F60" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="G60" s="3">
         <v>2100</v>
@@ -3336,42 +3475,45 @@
         <v>1800</v>
       </c>
       <c r="K60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>1900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1900</v>
+        <v>3200</v>
       </c>
       <c r="E61" s="3">
         <v>1900</v>
@@ -3392,37 +3534,40 @@
         <v>20200</v>
       </c>
       <c r="K61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="L61" s="3">
         <v>24200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>24200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>60000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>57500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>70800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3432,8 +3577,8 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
@@ -3448,22 +3593,22 @@
         <v>100</v>
       </c>
       <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -3475,10 +3620,13 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3533,8 +3681,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3589,8 +3740,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3645,19 +3799,22 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3500</v>
+        <v>5400</v>
       </c>
       <c r="E66" s="3">
         <v>3500</v>
       </c>
       <c r="F66" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="G66" s="3">
         <v>4000</v>
@@ -3672,37 +3829,40 @@
         <v>22000</v>
       </c>
       <c r="K66" s="3">
+        <v>22000</v>
+      </c>
+      <c r="L66" s="3">
         <v>27000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>27000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>81100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>79400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>76300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>76800</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3723,8 +3883,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3779,8 +3940,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3835,8 +3999,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3891,8 +4058,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3947,19 +4117,22 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-125800</v>
+        <v>-124300</v>
       </c>
       <c r="E72" s="3">
         <v>-125800</v>
       </c>
       <c r="F72" s="3">
-        <v>-121700</v>
+        <v>-125800</v>
       </c>
       <c r="G72" s="3">
         <v>-121700</v>
@@ -3974,37 +4147,40 @@
         <v>-122300</v>
       </c>
       <c r="K72" s="3">
+        <v>-122300</v>
+      </c>
+      <c r="L72" s="3">
         <v>-123100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-119400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-123100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-119400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-383300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-387000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-374200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-364800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-354000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4059,8 +4235,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4115,8 +4294,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4171,19 +4353,22 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2500</v>
+        <v>6100</v>
       </c>
       <c r="E76" s="3">
         <v>2500</v>
       </c>
       <c r="F76" s="3">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="G76" s="3">
         <v>2200</v>
@@ -4198,37 +4383,40 @@
         <v>-4600</v>
       </c>
       <c r="K76" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L76" s="3">
         <v>-7100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-4800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>-7100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-4800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4283,27 +4471,30 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45747</v>
       </c>
       <c r="H80" s="2">
         <v>45657</v>
@@ -4315,42 +4506,45 @@
         <v>45291</v>
       </c>
       <c r="K80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="E81" s="3">
         <v>-2100</v>
@@ -4359,7 +4553,7 @@
         <v>-2100</v>
       </c>
       <c r="G81" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="H81" s="3">
         <v>-2200</v>
@@ -4371,37 +4565,40 @@
         <v>-2300</v>
       </c>
       <c r="K81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4422,8 +4619,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4452,34 +4650,37 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>-100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
         <v>-2300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4534,8 +4735,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4590,8 +4794,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4646,8 +4853,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4702,8 +4912,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4758,22 +4971,25 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1700</v>
+        <v>-2500</v>
       </c>
       <c r="E89" s="3">
         <v>-1700</v>
       </c>
       <c r="F89" s="3">
-        <v>-1300</v>
+        <v>-1700</v>
       </c>
       <c r="G89" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="H89" s="3">
         <v>-1100</v>
@@ -4785,37 +5001,40 @@
         <v>-1200</v>
       </c>
       <c r="K89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>23400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4836,13 +5055,14 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -4863,37 +5083,40 @@
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4948,8 +5171,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5004,13 +5230,16 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -5031,37 +5260,40 @@
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5082,8 +5314,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5123,8 +5356,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5138,8 +5371,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5194,8 +5430,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5250,8 +5489,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5306,22 +5548,25 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="E100" s="3">
         <v>2100</v>
       </c>
       <c r="F100" s="3">
-        <v>800</v>
+        <v>2100</v>
       </c>
       <c r="G100" s="3">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="H100" s="3">
         <v>2000</v>
@@ -5332,8 +5577,8 @@
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
@@ -5347,23 +5592,26 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>6800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>-67800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5389,51 +5637,54 @@
         <v>-500</v>
       </c>
       <c r="K101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="E102" s="3">
         <v>300</v>
       </c>
       <c r="F102" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="G102" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>900</v>
@@ -5445,33 +5696,36 @@
         <v>-1500</v>
       </c>
       <c r="K102" s="3">
-        <v>-3300</v>
+        <v>-1500</v>
       </c>
       <c r="L102" s="3">
         <v>-3300</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="N102" s="3">
-        <v>-3300</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
         <v>-3300</v>
       </c>
       <c r="P102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q102" s="3">
         <v>5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>-46600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5200</v>
       </c>
     </row>
